--- a/astro-site/public/dl/kit-tareas-asador/BONUS-02-calendario-anual.xlsx
+++ b/astro-site/public/dl/kit-tareas-asador/BONUS-02-calendario-anual.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -516,14 +518,15 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -531,6 +534,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -538,6 +542,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -559,6 +564,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -566,6 +572,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -594,6 +601,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -601,8 +609,25 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-asador · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -611,7 +636,7 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -645,6 +670,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -915,6 +941,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -1123,6 +1150,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
@@ -1281,6 +1309,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
@@ -1408,6 +1437,8 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
@@ -1419,6 +1450,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>